--- a/input/index_Template.xlsx
+++ b/input/index_Template.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/00116505_uwa_edu_au/Documents/Desktop/NovaCAnton_Anth28S_qPCR_setup_pooling-main/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\00069749\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{1AD8115E-F438-4831-B198-FD41D6EA57B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C52FB1DD-243E-485C-B948-F22D47243763}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33D4662-D4E5-4A3D-A45D-B583A9ABDBAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-90" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{4F2E3ACD-65A3-4781-BB8A-039CB6C2BB4D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4F2E3ACD-65A3-4781-BB8A-039CB6C2BB4D}"/>
   </bookViews>
   <sheets>
-    <sheet name="16S_index" sheetId="2" r:id="rId1"/>
+    <sheet name="16SFishD_index" sheetId="2" r:id="rId1"/>
     <sheet name="MiFishU_index" sheetId="3" r:id="rId2"/>
     <sheet name="MiFishE2_index" sheetId="4" r:id="rId3"/>
     <sheet name="MiFishUE2_index" sheetId="7" r:id="rId4"/>
@@ -13234,17 +13234,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8776adc8-282a-4073-b44b-e3b5ad797728">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="e19eda2f-2a61-44e3-a391-8f02abd9f5ab" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010016C82931803BF94684D62330E359ACE7" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d83954054e138fb8dbf45a0ef3e5f22a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8776adc8-282a-4073-b44b-e3b5ad797728" xmlns:ns3="e19eda2f-2a61-44e3-a391-8f02abd9f5ab" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4539317776363280685762f2905da31a" ns2:_="" ns3:_="">
     <xsd:import namespace="8776adc8-282a-4073-b44b-e3b5ad797728"/>
@@ -13485,6 +13474,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8776adc8-282a-4073-b44b-e3b5ad797728">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="e19eda2f-2a61-44e3-a391-8f02abd9f5ab" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B9FCAA8-CD1F-49A3-8FC1-2BC65AC36FA3}">
   <ds:schemaRefs>
@@ -13494,6 +13494,25 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{170876D0-3EBF-4E75-9969-0D5F7D50C50F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8776adc8-282a-4073-b44b-e3b5ad797728"/>
+    <ds:schemaRef ds:uri="e19eda2f-2a61-44e3-a391-8f02abd9f5ab"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E6E1250-7A19-4909-AB3F-A88FCBAC8A78}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -13502,8 +13521,4 @@
     <ds:schemaRef ds:uri="e19eda2f-2a61-44e3-a391-8f02abd9f5ab"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{170876D0-3EBF-4E75-9969-0D5F7D50C50F}"/>
 </file>